--- a/KatalonData/RADTestData/ChangePaymentMethod.xlsx
+++ b/KatalonData/RADTestData/ChangePaymentMethod.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="587">
   <si>
     <t>Result</t>
   </si>
@@ -717,12 +717,1102 @@
   </si>
   <si>
     <t>Sun Aug 02 21:47:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 20:46:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 20:48:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 20:49:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 20:50:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 20:51:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 20:52:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 20:53:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 20:54:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 20:56:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 20:57:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 20:59:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:00:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:02:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:03:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:04:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:06:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:07:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:08:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:09:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:10:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:11:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:12:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:13:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:14:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:16:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:17:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:18:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:20:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:21:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:22:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:23:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:24:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:26:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:27:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:28:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:29:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:30:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:31:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:32:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:33:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:35:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:36:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:37:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:38:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:39:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:41:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:42:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:44:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:45:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:46:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:47:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:48:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:49:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:50:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:51:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:52:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:53:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:54:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:55:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:57:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:58:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 21:59:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:00:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:01:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:02:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:03:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:03:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:04:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:05:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:06:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:07:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:08:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:09:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:10:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:11:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:12:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:13:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:14:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:15:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:16:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:17:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:18:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:19:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:20:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:21:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:22:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:23:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:24:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:25:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:26:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:26:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:27:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:28:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:29:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:30:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:31:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:32:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:33:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:34:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:35:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:36:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:38:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:39:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:40:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:41:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:42:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:43:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:44:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:45:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:46:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:47:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:48:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:49:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:50:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:51:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:52:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:53:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:54:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:55:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:56:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:57:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:58:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 22:59:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:00:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:01:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:03:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:04:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:05:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:06:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:07:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:08:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:09:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:10:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:12:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:13:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:14:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:15:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:16:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:17:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:18:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:19:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:20:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:22:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:23:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:23:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:24:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:25:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:26:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:27:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:28:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:29:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:30:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:31:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:32:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:33:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:34:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:35:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:36:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:37:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:38:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:39:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:40:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:41:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:42:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:43:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:44:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:45:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:46:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:47:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:48:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:49:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:50:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:51:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:52:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:53:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:54:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:55:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:56:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:57:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:58:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 23:59:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:00:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:01:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:02:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:03:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:04:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:05:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:06:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:07:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:08:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:09:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:10:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:11:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:12:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:13:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:14:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:15:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:16:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:17:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:18:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:19:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:20:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:21:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:22:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:23:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:24:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:25:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:26:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:27:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:28:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:29:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:30:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:31:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:32:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:33:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:34:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:35:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:36:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:37:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:38:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:39:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:40:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:42:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:43:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:44:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:45:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:46:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:47:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:48:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:49:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:50:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:51:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:52:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:53:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:55:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:56:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:57:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:58:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 00:59:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:00:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:02:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:03:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:05:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:06:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:06:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:07:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:08:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:09:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:11:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:12:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:13:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:14:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:15:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:16:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:17:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:19:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:20:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:21:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:22:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:24:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:25:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:27:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:28:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:29:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:30:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:31:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:32:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:33:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:34:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:35:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:36:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:37:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:38:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:39:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:40:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:42:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:43:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:44:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:45:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:46:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:47:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:48:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:49:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:50:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:50:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:51:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:52:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:53:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:54:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:55:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:56:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:58:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 01:59:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:00:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:01:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:02:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:03:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:04:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:05:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:06:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:07:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:08:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 02:09:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 18:47:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 18:49:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 18:50:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 18:51:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 18:52:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 18:53:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 18:54:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 18:55:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 18:56:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 18:57:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 18:58:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 18:59:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:00:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:01:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:02:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:03:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:04:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:05:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:06:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:07:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:08:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:09:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:10:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:11:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:12:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:14:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:15:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:18:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:19:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:21:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:22:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:23:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:24:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:25:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:27:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:28:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:30:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:31:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:33:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:35:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:36:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:37:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:38:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:39:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:40:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:41:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:42:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:43:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:44:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:45:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:46:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:47:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:48:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:49:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:50:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:51:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:52:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:53:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:54:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 19:55:46 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1095,17 +2185,17 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1145,7 +2235,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>224</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1174,7 +2264,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1203,7 +2293,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>226</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1235,7 +2325,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>121</v>
+        <v>227</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1267,7 +2357,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>122</v>
+        <v>228</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1299,7 +2389,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1331,7 +2421,7 @@
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1364,16 +2454,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1413,7 +2503,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>125</v>
+        <v>249</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1436,7 +2526,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>250</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1459,7 +2549,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>127</v>
+        <v>251</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1482,7 +2572,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>128</v>
+        <v>252</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1508,7 +2598,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>129</v>
+        <v>253</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1534,7 +2624,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1557,7 +2647,7 @@
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>131</v>
+        <v>255</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1580,7 +2670,7 @@
         <v>114</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>132</v>
+        <v>256</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -1603,7 +2693,7 @@
         <v>114</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>133</v>
+        <v>257</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -1626,7 +2716,7 @@
         <v>114</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>134</v>
+        <v>258</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -1649,7 +2739,7 @@
         <v>114</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>135</v>
+        <v>259</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -1672,7 +2762,7 @@
         <v>114</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>136</v>
+        <v>260</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -1695,7 +2785,7 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>137</v>
+        <v>261</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -1718,7 +2808,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -1738,7 +2828,7 @@
         <v>114</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>139</v>
+        <v>263</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -1764,7 +2854,7 @@
         <v>114</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>140</v>
+        <v>264</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -1787,7 +2877,7 @@
         <v>114</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>141</v>
+        <v>265</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -1827,7 +2917,7 @@
         <v>114</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>142</v>
+        <v>266</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -1872,15 +2962,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1917,7 +3007,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>143</v>
+        <v>267</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1943,7 +3033,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>144</v>
+        <v>268</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1966,7 +3056,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1992,7 +3082,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>146</v>
+        <v>270</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2018,7 +3108,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>147</v>
+        <v>271</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2044,7 +3134,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>148</v>
+        <v>272</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2079,17 +3169,17 @@
   <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="19.796875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.19921875" style="1" collapsed="1"/>
-    <col min="13" max="13" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="1" width="19.796875"/>
+    <col min="12" max="12" style="1" width="9.19921875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
+    <col min="14" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -2138,7 +3228,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>149</v>
+        <v>527</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2161,7 +3251,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>150</v>
+        <v>528</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2187,7 +3277,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>151</v>
+        <v>529</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2213,7 +3303,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>152</v>
+        <v>530</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2239,7 +3329,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>153</v>
+        <v>531</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2265,7 +3355,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>154</v>
+        <v>532</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2288,7 +3378,7 @@
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>155</v>
+        <v>533</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -2314,7 +3404,7 @@
         <v>114</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>156</v>
+        <v>534</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -2340,7 +3430,7 @@
         <v>114</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>157</v>
+        <v>535</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -2366,7 +3456,7 @@
         <v>114</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>158</v>
+        <v>536</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -2392,7 +3482,7 @@
         <v>114</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>159</v>
+        <v>537</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -2415,7 +3505,7 @@
         <v>114</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>160</v>
+        <v>538</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2441,7 +3531,7 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>161</v>
+        <v>539</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -2467,7 +3557,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>162</v>
+        <v>540</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2493,7 +3583,7 @@
         <v>114</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>163</v>
+        <v>541</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -2519,7 +3609,7 @@
         <v>114</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>164</v>
+        <v>542</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -2548,7 +3638,7 @@
         <v>114</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>165</v>
+        <v>543</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2577,7 +3667,7 @@
         <v>114</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>166</v>
+        <v>544</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
@@ -2606,7 +3696,7 @@
         <v>114</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>167</v>
+        <v>545</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2629,7 +3719,7 @@
         <v>114</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>168</v>
+        <v>546</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -2658,7 +3748,7 @@
         <v>114</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>169</v>
+        <v>547</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
@@ -2687,7 +3777,7 @@
         <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>170</v>
+        <v>548</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
@@ -2713,7 +3803,7 @@
         <v>114</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>171</v>
+        <v>549</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
@@ -2742,7 +3832,7 @@
         <v>114</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>172</v>
+        <v>550</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
@@ -2774,7 +3864,7 @@
         <v>114</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>173</v>
+        <v>551</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
@@ -2803,7 +3893,7 @@
         <v>114</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>174</v>
+        <v>552</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
@@ -2832,7 +3922,7 @@
         <v>114</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>175</v>
+        <v>553</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>29</v>
@@ -2864,7 +3954,7 @@
         <v>114</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>176</v>
+        <v>554</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
@@ -2893,7 +3983,7 @@
         <v>114</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>177</v>
+        <v>555</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
@@ -2922,7 +4012,7 @@
         <v>114</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>178</v>
+        <v>556</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>29</v>
@@ -2951,7 +4041,7 @@
         <v>114</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>179</v>
+        <v>557</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
@@ -2974,7 +4064,7 @@
         <v>114</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>180</v>
+        <v>558</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
@@ -3003,7 +4093,7 @@
         <v>114</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>181</v>
+        <v>559</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
@@ -3032,7 +4122,7 @@
         <v>114</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>182</v>
+        <v>560</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
@@ -3058,7 +4148,7 @@
         <v>114</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>183</v>
+        <v>561</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -3087,7 +4177,7 @@
         <v>114</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>184</v>
+        <v>562</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
@@ -3119,7 +4209,7 @@
         <v>114</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>185</v>
+        <v>563</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
@@ -3148,7 +4238,7 @@
         <v>114</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>186</v>
+        <v>564</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
@@ -3177,7 +4267,7 @@
         <v>114</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>187</v>
+        <v>565</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
@@ -3209,7 +4299,7 @@
         <v>114</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>188</v>
+        <v>566</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
@@ -3238,7 +4328,7 @@
         <v>114</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>189</v>
+        <v>567</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -3267,7 +4357,7 @@
         <v>114</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>190</v>
+        <v>568</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
@@ -3296,7 +4386,7 @@
         <v>114</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>191</v>
+        <v>569</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
@@ -3319,7 +4409,7 @@
         <v>114</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>192</v>
+        <v>570</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>29</v>
@@ -3348,7 +4438,7 @@
         <v>114</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>193</v>
+        <v>571</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -3377,7 +4467,7 @@
         <v>114</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>194</v>
+        <v>572</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
@@ -3403,7 +4493,7 @@
         <v>114</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>195</v>
+        <v>573</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>29</v>
@@ -3432,7 +4522,7 @@
         <v>114</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>196</v>
+        <v>574</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>29</v>
@@ -3464,7 +4554,7 @@
         <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>197</v>
+        <v>575</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>29</v>
@@ -3493,7 +4583,7 @@
         <v>114</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>198</v>
+        <v>576</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>29</v>
@@ -3522,7 +4612,7 @@
         <v>114</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>199</v>
+        <v>577</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>29</v>
@@ -3554,7 +4644,7 @@
         <v>114</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>200</v>
+        <v>578</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>29</v>
@@ -3577,7 +4667,7 @@
         <v>114</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>218</v>
+        <v>579</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>29</v>
@@ -3623,7 +4713,7 @@
         <v>114</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>201</v>
+        <v>580</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>29</v>
@@ -3646,7 +4736,7 @@
         <v>114</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>219</v>
+        <v>581</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>29</v>
@@ -3692,7 +4782,7 @@
         <v>114</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>202</v>
+        <v>582</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>29</v>
@@ -3712,10 +4802,10 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>217</v>
+        <v>114</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>220</v>
+        <v>583</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>29</v>
@@ -3761,7 +4851,7 @@
         <v>114</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>203</v>
+        <v>584</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>29</v>
@@ -3787,7 +4877,7 @@
         <v>114</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>204</v>
+        <v>585</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>29</v>
@@ -3813,7 +4903,7 @@
         <v>114</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>205</v>
+        <v>586</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>29</v>
@@ -3849,14 +4939,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -3890,7 +4980,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>207</v>
+        <v>514</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -3913,7 +5003,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>208</v>
+        <v>515</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -3936,7 +5026,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>209</v>
+        <v>516</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -3959,7 +5049,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>210</v>
+        <v>517</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -3982,7 +5072,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>211</v>
+        <v>518</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4005,7 +5095,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>221</v>
+        <v>519</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -4025,7 +5115,7 @@
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>222</v>
+        <v>520</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -4044,8 +5134,8 @@
       <c r="A9" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B9" t="s">
-        <v>223</v>
+      <c r="B9" t="s" s="1">
+        <v>521</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -4070,14 +5160,14 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4108,7 +5198,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4131,7 +5221,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>213</v>
+        <v>523</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4154,7 +5244,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>214</v>
+        <v>524</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4177,7 +5267,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>215</v>
+        <v>525</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4200,7 +5290,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>216</v>
+        <v>526</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4228,12 +5318,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4261,7 +5351,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>206</v>
+        <v>513</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
